--- a/docs/Recipe-import-task/tracker-live-202.xlsx
+++ b/docs/Recipe-import-task/tracker-live-202.xlsx
@@ -588,12 +588,24 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>imported-awaiting-verify</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>anomaly-CCBAL-B1B.xlsx</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>GFF554R / GFF554R-S / GFF142R / GFF142R-S / GFF456MC</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>awaiting other agent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -617,12 +629,24 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>imported-awaiting-verify</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>anomaly-CCBAR1-R4TCC.xlsx</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>GFF333R / GFF333R-S / GFF143R-S / GFF394MC</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>awaiting other agent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -650,12 +674,24 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>imported-awaiting-verify</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>anomaly-CCBAR1-R4TEB.xlsx</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>GFF164R / GFF333R / GFF143R / GFF232MC</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>awaiting other agent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -679,12 +715,24 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>imported-awaiting-verify</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>anomaly-CCBTB-R1TEB.xlsx</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>GFF503R / GFF503R-S / GFF469MC</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>awaiting other agent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
